--- a/WorkBot/refactor-experimental/data/orders/Equal Exchange/Equal Exchange_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Equal Exchange/Equal Exchange_Collegetown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Tea Bags - Green (Equal Exchage)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>19.20</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>19.20</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Filter - Coffee</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Filter - Cold Brew (Silk)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>33.98</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>33.98</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Equal Exchange - One World</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>83.50</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>334.00</t>
-        </is>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>334</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Equal Exchange - Black Silk Espresso</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>83.50</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>584.50</t>
-        </is>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>584.5</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Equal Exchange - Espresso, Decaf</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>106.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>106.00</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>106</v>
+      </c>
+      <c r="E7" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Equal Exchange - Cold Brew</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>83.50</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>83.50</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>83.5</v>
       </c>
     </row>
   </sheetData>
